--- a/Battery Charger Project/Excel/Calculations/Component calcs.xlsx
+++ b/Battery Charger Project/Excel/Calculations/Component calcs.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Verrazano\Acedemic\Research\Battery-Charger\Battery Charger Project\Excel\Calculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5297D8D-99FC-44D4-9AEC-A30684E1A046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49D38EDC-B945-48A5-AF6D-F04D58DF9D98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8EA801AC-1218-4C2A-8BFC-BC5B39F04A2A}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{8EA801AC-1218-4C2A-8BFC-BC5B39F04A2A}"/>
   </bookViews>
   <sheets>
     <sheet name="24V analysis" sheetId="1" r:id="rId1"/>
     <sheet name="12V analysis" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -2398,6 +2398,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="77b6129a-f613-4ff9-b238-21504ab3c311" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009660838691862E40BA8A9FCF4672D404" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="57f0f8c66996a8cfd8079b5f5cbc1044">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="77b6129a-f613-4ff9-b238-21504ab3c311" xmlns:ns4="e5775723-78a2-49b3-980c-6ad0b4b03e58" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="97be24bc9c367c471a14e5d43da4af43" ns3:_="" ns4:_="">
     <xsd:import namespace="77b6129a-f613-4ff9-b238-21504ab3c311"/>
@@ -2586,38 +2603,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="77b6129a-f613-4ff9-b238-21504ab3c311" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F510E196-854A-4018-94EA-77433BC9C36C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D69E919-C42D-4F67-B937-7A9547F9358A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="77b6129a-f613-4ff9-b238-21504ab3c311"/>
-    <ds:schemaRef ds:uri="e5775723-78a2-49b3-980c-6ad0b4b03e58"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2640,9 +2629,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D69E919-C42D-4F67-B937-7A9547F9358A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F510E196-854A-4018-94EA-77433BC9C36C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="77b6129a-f613-4ff9-b238-21504ab3c311"/>
+    <ds:schemaRef ds:uri="e5775723-78a2-49b3-980c-6ad0b4b03e58"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>